--- a/Anexo_04_Estadisticas_post_limpieza/Anexo_04_Estadisticas_post_limpieza.xlsx
+++ b/Anexo_04_Estadisticas_post_limpieza/Anexo_04_Estadisticas_post_limpieza.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="2" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Estadísticas post limpieza" sheetId="1" state="visible" r:id="rId1"/>
@@ -368,7 +368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:M98"/>
+  <dimension ref="A2:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -1649,38 +1649,38 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>SRR26147265_clean</t>
+          <t>SRR26147254_clean</t>
         </is>
       </c>
       <c r="D33" s="4" t="n">
-        <v>11261</v>
+        <v>10922</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16005269</v>
+        <v>15521504</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1421.3</v>
+        <v>1421.12</v>
       </c>
       <c r="G33" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1629</v>
+        <v>1574</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>54.24</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>18.2</v>
+        <v>18.18</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.78</v>
+        <v>14.05</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>24.34</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="34">
@@ -1689,38 +1689,38 @@
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>SRR26147276_clean</t>
+          <t>SRR26147265_clean</t>
         </is>
       </c>
       <c r="D34" s="4" t="n">
-        <v>21600</v>
+        <v>11261</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>30692313</v>
+        <v>16005269</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1420.94</v>
+        <v>1421.3</v>
       </c>
       <c r="G34" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1625</v>
+        <v>1629</v>
       </c>
       <c r="I34" s="4" t="n">
         <v>1426</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>54.2</v>
+        <v>54.24</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>18.16</v>
+        <v>18.2</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>13.8</v>
+        <v>13.78</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>24.12</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="35">
@@ -1729,38 +1729,38 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>SRR26147286_clean</t>
+          <t>SRR26147276_clean</t>
         </is>
       </c>
       <c r="D35" s="4" t="n">
-        <v>7281</v>
+        <v>21600</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10391262</v>
+        <v>30692313</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1427.18</v>
+        <v>1420.94</v>
       </c>
       <c r="G35" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1593</v>
+        <v>1625</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>56.48</v>
+        <v>54.2</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>17.95</v>
+        <v>18.16</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>13.85</v>
+        <v>13.8</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>23.43</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="36">
@@ -1769,38 +1769,38 @@
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>SRR26147287_clean</t>
+          <t>SRR26147286_clean</t>
         </is>
       </c>
       <c r="D36" s="4" t="n">
-        <v>10411</v>
+        <v>7281</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>14869406</v>
+        <v>10391262</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1428.24</v>
+        <v>1427.18</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1626</v>
+        <v>1593</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>56.25</v>
+        <v>56.48</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>17.99</v>
+        <v>17.95</v>
       </c>
       <c r="L36" s="4" t="n">
-        <v>14</v>
+        <v>13.85</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>23.85</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="37">
@@ -1809,38 +1809,38 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>SRR26147288_clean</t>
+          <t>SRR26147287_clean</t>
         </is>
       </c>
       <c r="D37" s="4" t="n">
-        <v>14319</v>
+        <v>10411</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>20447437</v>
+        <v>14869406</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1427.99</v>
+        <v>1428.24</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1680</v>
+        <v>1626</v>
       </c>
       <c r="I37" s="4" t="n">
         <v>1433</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>56.37</v>
+        <v>56.25</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>17.96</v>
+        <v>17.99</v>
       </c>
       <c r="L37" s="4" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>23.82</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="38">
@@ -1849,38 +1849,38 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>SRR26147289_clean</t>
+          <t>SRR26147288_clean</t>
         </is>
       </c>
       <c r="D38" s="4" t="n">
-        <v>17921</v>
+        <v>14319</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>25582306</v>
+        <v>20447437</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1427.5</v>
+        <v>1427.99</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1641</v>
+        <v>1680</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>56.43</v>
+        <v>56.37</v>
       </c>
       <c r="K38" s="4" t="n">
         <v>17.96</v>
       </c>
       <c r="L38" s="4" t="n">
-        <v>13.76</v>
+        <v>13.8</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>23.66</v>
+        <v>23.82</v>
       </c>
     </row>
     <row r="39">
@@ -1889,38 +1889,38 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>SRR26147290_clean</t>
+          <t>SRR26147289_clean</t>
         </is>
       </c>
       <c r="D39" s="4" t="n">
-        <v>11818</v>
+        <v>17921</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>16874885</v>
+        <v>25582306</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1427.9</v>
+        <v>1427.5</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1694</v>
+        <v>1641</v>
       </c>
       <c r="I39" s="4" t="n">
         <v>1432</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>56.26</v>
+        <v>56.43</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>18.07</v>
+        <v>17.96</v>
       </c>
       <c r="L39" s="4" t="n">
-        <v>14.12</v>
+        <v>13.76</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>23.72</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="40">
@@ -1929,38 +1929,38 @@
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>SRR26147292_clean</t>
+          <t>SRR26147290_clean</t>
         </is>
       </c>
       <c r="D40" s="4" t="n">
-        <v>15141</v>
+        <v>11818</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>21620243</v>
+        <v>16874885</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1427.93</v>
+        <v>1427.9</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1591</v>
+        <v>1694</v>
       </c>
       <c r="I40" s="4" t="n">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>56.31</v>
+        <v>56.26</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>18.02</v>
+        <v>18.07</v>
       </c>
       <c r="L40" s="4" t="n">
-        <v>14.02</v>
+        <v>14.12</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>24.21</v>
+        <v>23.72</v>
       </c>
     </row>
     <row r="41">
@@ -1969,38 +1969,38 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>SRR26147303_clean</t>
+          <t>SRR26147292_clean</t>
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>8773</v>
+        <v>15141</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>12522816</v>
+        <v>21620243</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1427.43</v>
+        <v>1427.93</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1689</v>
+        <v>1591</v>
       </c>
       <c r="I41" s="4" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>56.56</v>
+        <v>56.31</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>18.02</v>
       </c>
       <c r="L41" s="4" t="n">
-        <v>13.84</v>
+        <v>14.02</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>23.84</v>
+        <v>24.21</v>
       </c>
     </row>
     <row r="42">
@@ -2009,38 +2009,38 @@
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>SRR26147314_clean</t>
+          <t>SRR26147303_clean</t>
         </is>
       </c>
       <c r="D42" s="4" t="n">
-        <v>20186</v>
+        <v>8773</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>28681956</v>
+        <v>12522816</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1420.88</v>
+        <v>1427.43</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>1681</v>
+        <v>1689</v>
       </c>
       <c r="I42" s="4" t="n">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>54.87</v>
+        <v>56.56</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>18.13</v>
+        <v>18.02</v>
       </c>
       <c r="L42" s="4" t="n">
-        <v>13.87</v>
+        <v>13.84</v>
       </c>
       <c r="M42" s="4" t="n">
-        <v>24.34</v>
+        <v>23.84</v>
       </c>
     </row>
     <row r="43">
@@ -2049,38 +2049,38 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>SRR26147329_clean</t>
+          <t>SRR26147314_clean</t>
         </is>
       </c>
       <c r="D43" s="4" t="n">
-        <v>9460</v>
+        <v>20186</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>13507706</v>
+        <v>28681956</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1427.88</v>
+        <v>1420.88</v>
       </c>
       <c r="G43" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>1690</v>
+        <v>1681</v>
       </c>
       <c r="I43" s="4" t="n">
-        <v>1433</v>
+        <v>1426</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>56.1</v>
+        <v>54.87</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>18.02</v>
+        <v>18.13</v>
       </c>
       <c r="L43" s="4" t="n">
-        <v>13.73</v>
+        <v>13.87</v>
       </c>
       <c r="M43" s="4" t="n">
-        <v>23.35</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="44">
@@ -2089,38 +2089,38 @@
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>SRR26147340_clean</t>
+          <t>SRR26147329_clean</t>
         </is>
       </c>
       <c r="D44" s="4" t="n">
-        <v>22427</v>
+        <v>9460</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>31997370</v>
+        <v>13507706</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1426.73</v>
+        <v>1427.88</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="I44" s="4" t="n">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>17.97</v>
+        <v>18.02</v>
       </c>
       <c r="L44" s="4" t="n">
-        <v>13.87</v>
+        <v>13.73</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>23.85</v>
+        <v>23.35</v>
       </c>
     </row>
     <row r="45">
@@ -2129,38 +2129,38 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>SRR26147351_clean</t>
+          <t>SRR26147340_clean</t>
         </is>
       </c>
       <c r="D45" s="4" t="n">
-        <v>13738</v>
+        <v>22427</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>19590972</v>
+        <v>31997370</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1426.04</v>
+        <v>1426.73</v>
       </c>
       <c r="G45" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>1653</v>
+        <v>1695</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>56.41</v>
+        <v>56.2</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>17.95</v>
+        <v>17.97</v>
       </c>
       <c r="L45" s="4" t="n">
-        <v>13.93</v>
+        <v>13.87</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>24.18</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="46">
@@ -2169,38 +2169,38 @@
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>SRR26147365_clean</t>
+          <t>SRR26147351_clean</t>
         </is>
       </c>
       <c r="D46" s="4" t="n">
-        <v>8282</v>
+        <v>13738</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>11777574</v>
+        <v>19590972</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1422.07</v>
+        <v>1426.04</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>1698</v>
+        <v>1653</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>1427</v>
+        <v>1431</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>54.28</v>
+        <v>56.41</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>18.24</v>
+        <v>17.95</v>
       </c>
       <c r="L46" s="4" t="n">
-        <v>13.99</v>
+        <v>13.93</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>23.53</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="47">
@@ -2209,38 +2209,38 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>SRR26147376_clean</t>
+          <t>SRR26147365_clean</t>
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>20984</v>
+        <v>8282</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>29835675</v>
+        <v>11777574</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1421.83</v>
+        <v>1422.07</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>54.29</v>
+        <v>54.28</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>18.14</v>
+        <v>18.24</v>
       </c>
       <c r="L47" s="4" t="n">
-        <v>13.57</v>
+        <v>13.99</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>23.83</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="48">
@@ -2249,38 +2249,38 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>SRR26147387_clean</t>
+          <t>SRR26147376_clean</t>
         </is>
       </c>
       <c r="D48" s="4" t="n">
-        <v>20462</v>
+        <v>20984</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>29256717</v>
+        <v>29835675</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1429.81</v>
+        <v>1421.83</v>
       </c>
       <c r="G48" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>1673</v>
+        <v>1696</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1435</v>
+        <v>1426</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>56.13</v>
+        <v>54.29</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>18</v>
+        <v>18.14</v>
       </c>
       <c r="L48" s="4" t="n">
-        <v>13.81</v>
+        <v>13.57</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>24.51</v>
+        <v>23.83</v>
       </c>
     </row>
     <row r="49">
@@ -2289,38 +2289,38 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>SRR26147388_clean</t>
+          <t>SRR26147387_clean</t>
         </is>
       </c>
       <c r="D49" s="4" t="n">
-        <v>14635</v>
+        <v>20462</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>20907003</v>
+        <v>29256717</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1428.56</v>
+        <v>1429.81</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>1620</v>
+        <v>1673</v>
       </c>
       <c r="I49" s="4" t="n">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>55.98</v>
+        <v>56.13</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>18.02</v>
+        <v>18</v>
       </c>
       <c r="L49" s="4" t="n">
-        <v>13.85</v>
+        <v>13.81</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>23.8</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="50">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>SRR26147389_clean</t>
+          <t>SRR26147388_clean</t>
         </is>
       </c>
       <c r="D50" s="4" t="n">
-        <v>13916</v>
+        <v>14635</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>19895163</v>
+        <v>20907003</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1429.66</v>
+        <v>1428.56</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>1001</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>1663</v>
+        <v>1620</v>
       </c>
       <c r="I50" s="4" t="n">
         <v>1434</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>56.26</v>
+        <v>55.98</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>18.01</v>
+        <v>18.02</v>
       </c>
       <c r="L50" s="4" t="n">
-        <v>13.8</v>
+        <v>13.85</v>
       </c>
       <c r="M50" s="4" t="n">
         <v>23.8</v>
@@ -2369,38 +2369,38 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>SRR26147390_clean</t>
+          <t>SRR26147389_clean</t>
         </is>
       </c>
       <c r="D51" s="4" t="n">
-        <v>16474</v>
+        <v>13916</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>23543153</v>
+        <v>19895163</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1429.11</v>
+        <v>1429.66</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>1607</v>
+        <v>1663</v>
       </c>
       <c r="I51" s="4" t="n">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>56.47</v>
+        <v>56.26</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>17.96</v>
+        <v>18.01</v>
       </c>
       <c r="L51" s="4" t="n">
-        <v>14.05</v>
+        <v>13.8</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>23.59</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="52">
@@ -2409,38 +2409,38 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>SRR26147391_clean</t>
+          <t>SRR26147390_clean</t>
         </is>
       </c>
       <c r="D52" s="4" t="n">
-        <v>16900</v>
+        <v>16474</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>24026322</v>
+        <v>23543153</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1421.68</v>
+        <v>1429.11</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>1681</v>
+        <v>1607</v>
       </c>
       <c r="I52" s="4" t="n">
-        <v>1427</v>
+        <v>1433</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>55.37</v>
+        <v>56.47</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>18.08</v>
+        <v>17.96</v>
       </c>
       <c r="L52" s="4" t="n">
-        <v>13.8</v>
+        <v>14.05</v>
       </c>
       <c r="M52" s="4" t="n">
-        <v>24.61</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="53">
@@ -2449,38 +2449,38 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>SRR26147392_clean</t>
+          <t>SRR26147391_clean</t>
         </is>
       </c>
       <c r="D53" s="4" t="n">
-        <v>9896</v>
+        <v>16900</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>14062291</v>
+        <v>24026322</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1421.01</v>
+        <v>1421.68</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="I53" s="4" t="n">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>55.43</v>
+        <v>55.37</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>18.14</v>
+        <v>18.08</v>
       </c>
       <c r="L53" s="4" t="n">
-        <v>14.05</v>
+        <v>13.8</v>
       </c>
       <c r="M53" s="4" t="n">
-        <v>24.17</v>
+        <v>24.61</v>
       </c>
     </row>
     <row r="54">
@@ -2489,38 +2489,38 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>SRR26147393_clean</t>
+          <t>SRR26147392_clean</t>
         </is>
       </c>
       <c r="D54" s="4" t="n">
-        <v>7415</v>
+        <v>9896</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>10552065</v>
+        <v>14062291</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1423.07</v>
+        <v>1421.01</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>1582</v>
+        <v>1682</v>
       </c>
       <c r="I54" s="4" t="n">
-        <v>1428</v>
+        <v>1426</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>55.43</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>18.1</v>
+        <v>18.14</v>
       </c>
       <c r="L54" s="4" t="n">
-        <v>14.01</v>
+        <v>14.05</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>23.54</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="55">
@@ -2529,38 +2529,38 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>SRR26147394_clean</t>
+          <t>SRR26147393_clean</t>
         </is>
       </c>
       <c r="D55" s="4" t="n">
-        <v>14885</v>
+        <v>7415</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>21238930</v>
+        <v>10552065</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1426.87</v>
+        <v>1423.07</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>1698</v>
+        <v>1582</v>
       </c>
       <c r="I55" s="4" t="n">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>56.21</v>
+        <v>55.43</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="L55" s="4" t="n">
-        <v>13.69</v>
+        <v>14.01</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>23.87</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="56">
@@ -2569,38 +2569,38 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>SRR26147395_clean</t>
+          <t>SRR26147394_clean</t>
         </is>
       </c>
       <c r="D56" s="4" t="n">
-        <v>11894</v>
+        <v>14885</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>16912701</v>
+        <v>21238930</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1421.95</v>
+        <v>1426.87</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="I56" s="4" t="n">
-        <v>1428</v>
+        <v>1432</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>55.45</v>
+        <v>56.21</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>18.09</v>
+        <v>18</v>
       </c>
       <c r="L56" s="4" t="n">
-        <v>13.8</v>
+        <v>13.69</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>23.42</v>
+        <v>23.87</v>
       </c>
     </row>
     <row r="57">
@@ -2609,38 +2609,38 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>SRR26147396_clean</t>
+          <t>SRR26147395_clean</t>
         </is>
       </c>
       <c r="D57" s="4" t="n">
-        <v>12929</v>
+        <v>11894</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>18393476</v>
+        <v>16912701</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1422.65</v>
+        <v>1421.95</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>1677</v>
+        <v>1697</v>
       </c>
       <c r="I57" s="4" t="n">
         <v>1428</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>55.61</v>
+        <v>55.45</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>18.07</v>
+        <v>18.09</v>
       </c>
       <c r="L57" s="4" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="M57" s="4" t="n">
-        <v>23.86</v>
+        <v>23.42</v>
       </c>
     </row>
     <row r="58">
@@ -2649,38 +2649,38 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>SRR26147397_clean</t>
+          <t>SRR26147396_clean</t>
         </is>
       </c>
       <c r="D58" s="4" t="n">
-        <v>10015</v>
+        <v>12929</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>14245262</v>
+        <v>18393476</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1422.39</v>
+        <v>1422.65</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>1697</v>
+        <v>1677</v>
       </c>
       <c r="I58" s="4" t="n">
         <v>1428</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>55.3</v>
+        <v>55.61</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>18.08</v>
+        <v>18.07</v>
       </c>
       <c r="L58" s="4" t="n">
-        <v>13.82</v>
+        <v>14</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>24.02</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="59">
@@ -2689,38 +2689,38 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>SRR26147398_clean</t>
+          <t>SRR26147397_clean</t>
         </is>
       </c>
       <c r="D59" s="4" t="n">
-        <v>11130</v>
+        <v>10015</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>15809267</v>
+        <v>14245262</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1420.42</v>
+        <v>1422.39</v>
       </c>
       <c r="G59" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>1690</v>
+        <v>1697</v>
       </c>
       <c r="I59" s="4" t="n">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>55.15</v>
+        <v>55.3</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>18.14</v>
+        <v>18.08</v>
       </c>
       <c r="L59" s="4" t="n">
-        <v>13.95</v>
+        <v>13.82</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>24.03</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="60">
@@ -2729,38 +2729,38 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>SRR26147399_clean</t>
+          <t>SRR26147398_clean</t>
         </is>
       </c>
       <c r="D60" s="4" t="n">
-        <v>13762</v>
+        <v>11130</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>19573464</v>
+        <v>15809267</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1422.28</v>
+        <v>1420.42</v>
       </c>
       <c r="G60" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>1657</v>
+        <v>1690</v>
       </c>
       <c r="I60" s="4" t="n">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>55.72</v>
+        <v>55.15</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>18.09</v>
+        <v>18.14</v>
       </c>
       <c r="L60" s="4" t="n">
-        <v>13.62</v>
+        <v>13.95</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>24.23</v>
+        <v>24.03</v>
       </c>
     </row>
     <row r="61">
@@ -2769,38 +2769,38 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>SRR26147400_clean</t>
+          <t>SRR26147399_clean</t>
         </is>
       </c>
       <c r="D61" s="4" t="n">
-        <v>11920</v>
+        <v>13762</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>17009568</v>
+        <v>19573464</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1426.98</v>
+        <v>1422.28</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>1615</v>
+        <v>1657</v>
       </c>
       <c r="I61" s="4" t="n">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>56.51</v>
+        <v>55.72</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>17.97</v>
+        <v>18.09</v>
       </c>
       <c r="L61" s="4" t="n">
-        <v>13.81</v>
+        <v>13.62</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>23.53</v>
+        <v>24.23</v>
       </c>
     </row>
     <row r="62">
@@ -2809,38 +2809,38 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>SRR26147401_clean</t>
+          <t>SRR26147400_clean</t>
         </is>
       </c>
       <c r="D62" s="4" t="n">
-        <v>10707</v>
+        <v>11920</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>15293923</v>
+        <v>17009568</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1428.4</v>
+        <v>1426.98</v>
       </c>
       <c r="G62" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>1678</v>
+        <v>1615</v>
       </c>
       <c r="I62" s="4" t="n">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>56.51</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>18.01</v>
+        <v>17.97</v>
       </c>
       <c r="L62" s="4" t="n">
-        <v>13.78</v>
+        <v>13.81</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>23.96</v>
+        <v>23.53</v>
       </c>
     </row>
     <row r="63">
@@ -2849,38 +2849,38 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>SRR26147402_clean</t>
+          <t>SRR26147401_clean</t>
         </is>
       </c>
       <c r="D63" s="4" t="n">
-        <v>11592</v>
+        <v>10707</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>16532299</v>
+        <v>15293923</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1426.18</v>
+        <v>1428.4</v>
       </c>
       <c r="G63" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>1668</v>
+        <v>1678</v>
       </c>
       <c r="I63" s="4" t="n">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>56.54</v>
+        <v>56.51</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>17.97</v>
+        <v>18.01</v>
       </c>
       <c r="L63" s="4" t="n">
-        <v>13.56</v>
+        <v>13.78</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>23.52</v>
+        <v>23.96</v>
       </c>
     </row>
     <row r="64">
@@ -2889,38 +2889,38 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>SRR26147403_clean</t>
+          <t>SRR26147402_clean</t>
         </is>
       </c>
       <c r="D64" s="4" t="n">
-        <v>15288</v>
+        <v>11592</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>21803671</v>
+        <v>16532299</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1426.2</v>
+        <v>1426.18</v>
       </c>
       <c r="G64" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1617</v>
+        <v>1668</v>
       </c>
       <c r="I64" s="4" t="n">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>56.36</v>
+        <v>56.54</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>17.99</v>
+        <v>17.97</v>
       </c>
       <c r="L64" s="4" t="n">
-        <v>13.74</v>
+        <v>13.56</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>23.86</v>
+        <v>23.52</v>
       </c>
     </row>
     <row r="65">
@@ -2929,38 +2929,38 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>SRR26147404_clean</t>
+          <t>SRR26147403_clean</t>
         </is>
       </c>
       <c r="D65" s="4" t="n">
-        <v>8747</v>
+        <v>15288</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>12491727</v>
+        <v>21803671</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1428.12</v>
+        <v>1426.2</v>
       </c>
       <c r="G65" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="I65" s="4" t="n">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>56.17</v>
+        <v>56.36</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>18.01</v>
+        <v>17.99</v>
       </c>
       <c r="L65" s="4" t="n">
-        <v>14.1</v>
+        <v>13.74</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>23.69</v>
+        <v>23.86</v>
       </c>
     </row>
     <row r="66">
@@ -2969,38 +2969,38 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>SRR26147405_clean</t>
+          <t>SRR26147404_clean</t>
         </is>
       </c>
       <c r="D66" s="4" t="n">
-        <v>7472</v>
+        <v>8747</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>10656178</v>
+        <v>12491727</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1426.15</v>
+        <v>1428.12</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>1694</v>
+        <v>1619</v>
       </c>
       <c r="I66" s="4" t="n">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>56.12</v>
+        <v>56.17</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>18.04</v>
+        <v>18.01</v>
       </c>
       <c r="L66" s="4" t="n">
-        <v>13.74</v>
+        <v>14.1</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>23.73</v>
+        <v>23.69</v>
       </c>
     </row>
     <row r="67">
@@ -3009,38 +3009,38 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>SRR26147406_clean</t>
+          <t>SRR26147405_clean</t>
         </is>
       </c>
       <c r="D67" s="4" t="n">
-        <v>13070</v>
+        <v>7472</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>18663038</v>
+        <v>10656178</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1427.93</v>
+        <v>1426.15</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>1653</v>
+        <v>1694</v>
       </c>
       <c r="I67" s="4" t="n">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>56.22</v>
+        <v>56.12</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>18.02</v>
+        <v>18.04</v>
       </c>
       <c r="L67" s="4" t="n">
-        <v>13.34</v>
+        <v>13.74</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>24.88</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="68">
@@ -3049,38 +3049,38 @@
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>SRR26147407_clean</t>
+          <t>SRR26147406_clean</t>
         </is>
       </c>
       <c r="D68" s="4" t="n">
-        <v>13063</v>
+        <v>13070</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>18649760</v>
+        <v>18663038</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1427.68</v>
+        <v>1427.93</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>1591</v>
+        <v>1653</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>1433</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>56.34</v>
+        <v>56.22</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>18</v>
+        <v>18.02</v>
       </c>
       <c r="L68" s="4" t="n">
-        <v>14.04</v>
+        <v>13.34</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>24.24</v>
+        <v>24.88</v>
       </c>
     </row>
     <row r="69">
@@ -3089,38 +3089,38 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>SRR26147408_clean</t>
+          <t>SRR26147407_clean</t>
         </is>
       </c>
       <c r="D69" s="4" t="n">
-        <v>7420</v>
+        <v>13063</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>10600307</v>
+        <v>18649760</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1428.61</v>
+        <v>1427.68</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>1604</v>
+        <v>1591</v>
       </c>
       <c r="I69" s="4" t="n">
         <v>1433</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>56.4</v>
+        <v>56.34</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>18</v>
       </c>
       <c r="L69" s="4" t="n">
-        <v>13.97</v>
+        <v>14.04</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>24.04</v>
+        <v>24.24</v>
       </c>
     </row>
     <row r="70">
@@ -3129,38 +3129,38 @@
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>SRR26147409_clean</t>
+          <t>SRR26147408_clean</t>
         </is>
       </c>
       <c r="D70" s="4" t="n">
-        <v>13244</v>
+        <v>7420</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>18846780</v>
+        <v>10600307</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1423.04</v>
+        <v>1428.61</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1576</v>
+        <v>1604</v>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>55.4</v>
+        <v>56.4</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>18.11</v>
+        <v>18</v>
       </c>
       <c r="L70" s="4" t="n">
-        <v>13.81</v>
+        <v>13.97</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>24.22</v>
+        <v>24.04</v>
       </c>
     </row>
     <row r="71">
@@ -3169,38 +3169,38 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>SRR26147410_clean</t>
+          <t>SRR26147409_clean</t>
         </is>
       </c>
       <c r="D71" s="4" t="n">
-        <v>17544</v>
+        <v>13244</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>24929550</v>
+        <v>18846780</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1420.97</v>
+        <v>1423.04</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>1654</v>
+        <v>1576</v>
       </c>
       <c r="I71" s="4" t="n">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>55.32</v>
+        <v>55.4</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>18.07</v>
+        <v>18.11</v>
       </c>
       <c r="L71" s="4" t="n">
-        <v>13.82</v>
+        <v>13.81</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>23.85</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="72">
@@ -3209,38 +3209,38 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>SRR26147411_clean</t>
+          <t>SRR26147410_clean</t>
         </is>
       </c>
       <c r="D72" s="4" t="n">
-        <v>18664</v>
+        <v>17544</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>26520742</v>
+        <v>24929550</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1420.96</v>
+        <v>1420.97</v>
       </c>
       <c r="G72" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>1619</v>
+        <v>1654</v>
       </c>
       <c r="I72" s="4" t="n">
         <v>1427</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>55.28</v>
+        <v>55.32</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>18.11</v>
+        <v>18.07</v>
       </c>
       <c r="L72" s="4" t="n">
-        <v>13.76</v>
+        <v>13.82</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>24.62</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="73">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>SRR26147412_clean</t>
+          <t>SRR26147411_clean</t>
         </is>
       </c>
       <c r="D73" s="4" t="n">
-        <v>10487</v>
+        <v>18664</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>14911443</v>
+        <v>26520742</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1421.9</v>
+        <v>1420.96</v>
       </c>
       <c r="G73" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>1642</v>
+        <v>1619</v>
       </c>
       <c r="I73" s="4" t="n">
         <v>1427</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>55.25</v>
+        <v>55.28</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>18.13</v>
+        <v>18.11</v>
       </c>
       <c r="L73" s="4" t="n">
         <v>13.76</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>23.74</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="74">
@@ -3289,38 +3289,38 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>SRR26147413_clean</t>
+          <t>SRR26147412_clean</t>
         </is>
       </c>
       <c r="D74" s="4" t="n">
-        <v>15265</v>
+        <v>10487</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>21709363</v>
+        <v>14911443</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1422.17</v>
+        <v>1421.9</v>
       </c>
       <c r="G74" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1615</v>
+        <v>1642</v>
       </c>
       <c r="I74" s="4" t="n">
         <v>1427</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>55.3</v>
+        <v>55.25</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>18.07</v>
+        <v>18.13</v>
       </c>
       <c r="L74" s="4" t="n">
-        <v>13.96</v>
+        <v>13.76</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>23.54</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="75">
@@ -3329,38 +3329,38 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>SRR26147414_clean</t>
+          <t>SRR26147413_clean</t>
         </is>
       </c>
       <c r="D75" s="4" t="n">
-        <v>11031</v>
+        <v>15265</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>15691449</v>
+        <v>21709363</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1422.49</v>
+        <v>1422.17</v>
       </c>
       <c r="G75" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>1660</v>
+        <v>1615</v>
       </c>
       <c r="I75" s="4" t="n">
         <v>1427</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>55.22</v>
+        <v>55.3</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>18.08</v>
+        <v>18.07</v>
       </c>
       <c r="L75" s="4" t="n">
-        <v>13.94</v>
+        <v>13.96</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>23.37</v>
+        <v>23.54</v>
       </c>
     </row>
     <row r="76">
@@ -3369,38 +3369,38 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>SRR26147415_clean</t>
+          <t>SRR26147414_clean</t>
         </is>
       </c>
       <c r="D76" s="4" t="n">
-        <v>9261</v>
+        <v>11031</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>13157984</v>
+        <v>15691449</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1420.8</v>
+        <v>1422.49</v>
       </c>
       <c r="G76" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1611</v>
+        <v>1660</v>
       </c>
       <c r="I76" s="4" t="n">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>55.07</v>
+        <v>55.22</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>18.12</v>
+        <v>18.08</v>
       </c>
       <c r="L76" s="4" t="n">
-        <v>14.07</v>
+        <v>13.94</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>24.57</v>
+        <v>23.37</v>
       </c>
     </row>
     <row r="77">
@@ -3409,38 +3409,38 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>SRR26147416_clean</t>
+          <t>SRR26147415_clean</t>
         </is>
       </c>
       <c r="D77" s="4" t="n">
-        <v>6522</v>
+        <v>9261</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>9306586</v>
+        <v>13157984</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1426.95</v>
+        <v>1420.8</v>
       </c>
       <c r="G77" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>1651</v>
+        <v>1611</v>
       </c>
       <c r="I77" s="4" t="n">
-        <v>1432</v>
+        <v>1426</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>56.27</v>
+        <v>55.07</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>17.96</v>
+        <v>18.12</v>
       </c>
       <c r="L77" s="4" t="n">
-        <v>13.97</v>
+        <v>14.07</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>23.62</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="78">
@@ -3449,38 +3449,38 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>SRR26147417_clean</t>
+          <t>SRR26147416_clean</t>
         </is>
       </c>
       <c r="D78" s="4" t="n">
-        <v>22559</v>
+        <v>6522</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>32090360</v>
+        <v>9306586</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1422.51</v>
+        <v>1426.95</v>
       </c>
       <c r="G78" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>1690</v>
+        <v>1651</v>
       </c>
       <c r="I78" s="4" t="n">
-        <v>1427</v>
+        <v>1432</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>55.48</v>
+        <v>56.27</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>18.08</v>
+        <v>17.96</v>
       </c>
       <c r="L78" s="4" t="n">
-        <v>13.67</v>
+        <v>13.97</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>24.62</v>
+        <v>23.62</v>
       </c>
     </row>
     <row r="79">
@@ -3489,38 +3489,38 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>SRR26147418_clean</t>
+          <t>SRR26147417_clean</t>
         </is>
       </c>
       <c r="D79" s="4" t="n">
-        <v>17018</v>
+        <v>22559</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>24282319</v>
+        <v>32090360</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1426.86</v>
+        <v>1422.51</v>
       </c>
       <c r="G79" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>1661</v>
+        <v>1690</v>
       </c>
       <c r="I79" s="4" t="n">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>56.64</v>
+        <v>55.48</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>17.99</v>
+        <v>18.08</v>
       </c>
       <c r="L79" s="4" t="n">
-        <v>13.98</v>
+        <v>13.67</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>24.11</v>
+        <v>24.62</v>
       </c>
     </row>
     <row r="80">
@@ -3529,38 +3529,38 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>SRR26147421_clean</t>
+          <t>SRR26147418_clean</t>
         </is>
       </c>
       <c r="D80" s="4" t="n">
-        <v>18566</v>
+        <v>17018</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>26373408</v>
+        <v>24282319</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1420.52</v>
+        <v>1426.86</v>
       </c>
       <c r="G80" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>1696</v>
+        <v>1661</v>
       </c>
       <c r="I80" s="4" t="n">
-        <v>1426</v>
+        <v>1432</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>54.77</v>
+        <v>56.64</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>18.14</v>
+        <v>17.99</v>
       </c>
       <c r="L80" s="4" t="n">
-        <v>14.05</v>
+        <v>13.98</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>24.38</v>
+        <v>24.11</v>
       </c>
     </row>
     <row r="81">
@@ -3569,38 +3569,38 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>SRR26147432_clean</t>
+          <t>SRR26147421_clean</t>
         </is>
       </c>
       <c r="D81" s="4" t="n">
-        <v>15484</v>
+        <v>18566</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>22010543</v>
+        <v>26373408</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1421.5</v>
+        <v>1420.52</v>
       </c>
       <c r="G81" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1639</v>
+        <v>1696</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>54.94</v>
+        <v>54.77</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>18.11</v>
+        <v>18.14</v>
       </c>
       <c r="L81" s="4" t="n">
-        <v>13.99</v>
+        <v>14.05</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>24.23</v>
+        <v>24.38</v>
       </c>
     </row>
     <row r="82">
@@ -3609,38 +3609,38 @@
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>SRR26147443_clean</t>
+          <t>SRR26147432_clean</t>
         </is>
       </c>
       <c r="D82" s="4" t="n">
-        <v>10236</v>
+        <v>15484</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>14551372</v>
+        <v>22010543</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1421.59</v>
+        <v>1421.5</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>1682</v>
+        <v>1639</v>
       </c>
       <c r="I82" s="4" t="n">
         <v>1427</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>54.93</v>
+        <v>54.94</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>18.11</v>
       </c>
       <c r="L82" s="4" t="n">
-        <v>13.63</v>
+        <v>13.99</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>24.96</v>
+        <v>24.23</v>
       </c>
     </row>
     <row r="83">
@@ -3649,38 +3649,38 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>SRR26147458_clean</t>
+          <t>SRR26147443_clean</t>
         </is>
       </c>
       <c r="D83" s="4" t="n">
-        <v>11499</v>
+        <v>10236</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>16427472</v>
+        <v>14551372</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1428.6</v>
+        <v>1421.59</v>
       </c>
       <c r="G83" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>1622</v>
+        <v>1682</v>
       </c>
       <c r="I83" s="4" t="n">
-        <v>1433</v>
+        <v>1427</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>56.27</v>
+        <v>54.93</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>18.03</v>
+        <v>18.11</v>
       </c>
       <c r="L83" s="4" t="n">
-        <v>13.74</v>
+        <v>13.63</v>
       </c>
       <c r="M83" s="4" t="n">
-        <v>23.78</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="84">
@@ -3689,38 +3689,38 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>SRR26147469_clean</t>
+          <t>SRR26147458_clean</t>
         </is>
       </c>
       <c r="D84" s="4" t="n">
-        <v>11433</v>
+        <v>11499</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>16329263</v>
+        <v>16427472</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1428.26</v>
+        <v>1428.6</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>1584</v>
+        <v>1622</v>
       </c>
       <c r="I84" s="4" t="n">
         <v>1433</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>56.49</v>
+        <v>56.27</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>18</v>
+        <v>18.03</v>
       </c>
       <c r="L84" s="4" t="n">
-        <v>13.78</v>
+        <v>13.74</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>23.51</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="85">
@@ -3729,38 +3729,38 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>SRR26147470_clean</t>
+          <t>SRR26147469_clean</t>
         </is>
       </c>
       <c r="D85" s="4" t="n">
-        <v>7705</v>
+        <v>11433</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>11128785</v>
+        <v>16329263</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1444.36</v>
+        <v>1428.26</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="I85" s="4" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>54.85</v>
+        <v>56.49</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>17.98</v>
+        <v>18</v>
       </c>
       <c r="L85" s="4" t="n">
-        <v>13.68</v>
+        <v>13.78</v>
       </c>
       <c r="M85" s="4" t="n">
-        <v>23.32</v>
+        <v>23.51</v>
       </c>
     </row>
     <row r="86">
@@ -3769,38 +3769,38 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>SRR26147481_clean</t>
+          <t>SRR26147470_clean</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>10820</v>
+        <v>7705</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>15462723</v>
+        <v>11128785</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1429.09</v>
+        <v>1444.36</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1596</v>
+        <v>1585</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>1434</v>
+        <v>1445</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>56.63</v>
+        <v>54.85</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>17.99</v>
+        <v>17.98</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>13.96</v>
+        <v>13.68</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>23.3</v>
+        <v>23.32</v>
       </c>
     </row>
     <row r="87">
@@ -3809,38 +3809,38 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>SRR26147483_clean</t>
+          <t>SRR26147481_clean</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>12492</v>
+        <v>10820</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>17748216</v>
+        <v>15462723</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1420.77</v>
+        <v>1429.09</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1631</v>
+        <v>1596</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1426</v>
+        <v>1434</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>54.17</v>
+        <v>56.63</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>18.19</v>
+        <v>17.99</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>13.79</v>
+        <v>13.96</v>
       </c>
       <c r="M87" s="4" t="n">
-        <v>24.16</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="88">
@@ -3849,38 +3849,38 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>SRR26147494_clean</t>
+          <t>SRR26147483_clean</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>15742</v>
+        <v>12492</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>22360870</v>
+        <v>17748216</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1420.46</v>
+        <v>1420.77</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1579</v>
+        <v>1631</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>54.13</v>
+        <v>54.17</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>18.16</v>
+        <v>18.19</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>13.82</v>
+        <v>13.79</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>24.2</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="89">
@@ -3889,374 +3889,414 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>SRR26147505_clean</t>
+          <t>SRR26147494_clean</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>14426</v>
+        <v>15742</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>20508853</v>
+        <v>22360870</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1421.66</v>
+        <v>1420.46</v>
       </c>
       <c r="G89" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1628</v>
+        <v>1579</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>54.3</v>
+        <v>54.13</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>18.19</v>
+        <v>18.16</v>
       </c>
       <c r="L89" s="4" t="n">
         <v>13.82</v>
       </c>
       <c r="M89" s="4" t="n">
-        <v>24.33</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="11" t="n">
         <v>88</v>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>SRR26147505_clean</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>14426</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>20508853</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>1421.66</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>1628</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>1426</v>
+      </c>
+      <c r="J90" s="4" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="K90" s="4" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L90" s="4" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="M90" s="4" t="n">
+        <v>24.33</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>SRR26147516_clean</t>
         </is>
       </c>
-      <c r="D90" s="9" t="n">
+      <c r="D91" s="9" t="n">
         <v>20705</v>
       </c>
-      <c r="E90" s="9" t="n">
+      <c r="E91" s="9" t="n">
         <v>29564278</v>
       </c>
-      <c r="F90" s="9" t="n">
+      <c r="F91" s="9" t="n">
         <v>1427.88</v>
       </c>
-      <c r="G90" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H90" s="9" t="n">
+      <c r="G91" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H91" s="9" t="n">
         <v>1696</v>
       </c>
-      <c r="I90" s="9" t="n">
+      <c r="I91" s="9" t="n">
         <v>1432</v>
       </c>
-      <c r="J90" s="9" t="n">
+      <c r="J91" s="9" t="n">
         <v>56.56</v>
       </c>
-      <c r="K90" s="9" t="n">
+      <c r="K91" s="9" t="n">
         <v>17.94</v>
       </c>
-      <c r="L90" s="9" t="n">
+      <c r="L91" s="9" t="n">
         <v>13.91</v>
       </c>
-      <c r="M90" s="9" t="n">
+      <c r="M91" s="9" t="n">
         <v>23.93</v>
       </c>
     </row>
-    <row r="91">
-      <c r="C91" s="11" t="inlineStr">
+    <row r="92">
+      <c r="C92" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D91" s="10">
-        <f>SUM(D3:D90)</f>
+      <c r="D92" s="10">
+        <f>SUM(D3:D91)</f>
         <v/>
       </c>
-      <c r="E91" s="10">
-        <f>SUM(E3:E90)</f>
+      <c r="E92" s="10">
+        <f>SUM(E3:E91)</f>
         <v/>
       </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="F92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H91" s="10" t="inlineStr">
+      <c r="H92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="10" t="inlineStr">
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J91" s="10" t="inlineStr">
+      <c r="J92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K91" s="10" t="inlineStr">
+      <c r="K92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L91" s="10" t="inlineStr">
+      <c r="L92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M91" s="10" t="inlineStr">
+      <c r="M92" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="C92" s="12" t="n"/>
-      <c r="D92" s="12" t="n"/>
-      <c r="E92" s="12" t="n"/>
-      <c r="F92" s="12" t="n"/>
-      <c r="G92" s="12" t="n"/>
-      <c r="H92" s="12" t="n"/>
-      <c r="I92" s="12" t="n"/>
-      <c r="J92" s="12" t="n"/>
-      <c r="K92" s="12" t="n"/>
-      <c r="L92" s="12" t="n"/>
-      <c r="M92" s="12" t="n"/>
-    </row>
     <row r="93">
-      <c r="C93" s="11" t="inlineStr">
+      <c r="C93" s="12" t="n"/>
+      <c r="D93" s="12" t="n"/>
+      <c r="E93" s="12" t="n"/>
+      <c r="F93" s="12" t="n"/>
+      <c r="G93" s="12" t="n"/>
+      <c r="H93" s="12" t="n"/>
+      <c r="I93" s="12" t="n"/>
+      <c r="J93" s="12" t="n"/>
+      <c r="K93" s="12" t="n"/>
+      <c r="L93" s="12" t="n"/>
+      <c r="M93" s="12" t="n"/>
+    </row>
+    <row r="94">
+      <c r="C94" s="11" t="inlineStr">
         <is>
           <t>PROMEDIO</t>
         </is>
       </c>
-      <c r="D93" s="10">
-        <f>AVERAGE(D3:D90)</f>
+      <c r="D94" s="10">
+        <f>AVERAGE(D3:D91)</f>
         <v/>
       </c>
-      <c r="E93" s="10">
-        <f>AVERAGE(E3:E90)</f>
+      <c r="E94" s="10">
+        <f>AVERAGE(E3:E91)</f>
         <v/>
       </c>
-      <c r="F93" s="10">
-        <f>AVERAGE(F3:F90)</f>
+      <c r="F94" s="10">
+        <f>AVERAGE(F3:F91)</f>
         <v/>
       </c>
-      <c r="G93" s="10">
-        <f>AVERAGE(G3:G90)</f>
+      <c r="G94" s="10">
+        <f>AVERAGE(G3:G91)</f>
         <v/>
       </c>
-      <c r="H93" s="10">
-        <f>AVERAGE(H3:H90)</f>
+      <c r="H94" s="10">
+        <f>AVERAGE(H3:H91)</f>
         <v/>
       </c>
-      <c r="I93" s="10">
-        <f>AVERAGE(I3:I90)</f>
+      <c r="I94" s="10">
+        <f>AVERAGE(I3:I91)</f>
         <v/>
       </c>
-      <c r="J93" s="10">
-        <f>AVERAGE(J3:J90)</f>
+      <c r="J94" s="10">
+        <f>AVERAGE(J3:J91)</f>
         <v/>
       </c>
-      <c r="K93" s="10">
-        <f>AVERAGE(K3:K90)</f>
+      <c r="K94" s="10">
+        <f>AVERAGE(K3:K91)</f>
         <v/>
       </c>
-      <c r="L93" s="10">
-        <f>AVERAGE(L3:L90)</f>
+      <c r="L94" s="10">
+        <f>AVERAGE(L3:L91)</f>
         <v/>
       </c>
-      <c r="M93" s="10">
-        <f>AVERAGE(M3:M90)</f>
+      <c r="M94" s="10">
+        <f>AVERAGE(M3:M91)</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
-      <c r="E94" s="12" t="n"/>
-      <c r="F94" s="12" t="n"/>
-      <c r="G94" s="12" t="n"/>
-      <c r="H94" s="12" t="n"/>
-      <c r="I94" s="12" t="n"/>
-      <c r="J94" s="12" t="n"/>
-      <c r="K94" s="12" t="n"/>
-      <c r="L94" s="12" t="n"/>
-      <c r="M94" s="12" t="n"/>
-    </row>
     <row r="95">
-      <c r="C95" s="11" t="inlineStr">
+      <c r="C95" s="12" t="n"/>
+      <c r="D95" s="12" t="n"/>
+      <c r="E95" s="12" t="n"/>
+      <c r="F95" s="12" t="n"/>
+      <c r="G95" s="12" t="n"/>
+      <c r="H95" s="12" t="n"/>
+      <c r="I95" s="12" t="n"/>
+      <c r="J95" s="12" t="n"/>
+      <c r="K95" s="12" t="n"/>
+      <c r="L95" s="12" t="n"/>
+      <c r="M95" s="12" t="n"/>
+    </row>
+    <row r="96">
+      <c r="C96" s="11" t="inlineStr">
         <is>
           <t>MÁXIMO</t>
         </is>
       </c>
-      <c r="D95" s="10">
-        <f>MAX(D3:D90)</f>
+      <c r="D96" s="10">
+        <f>MAX(D3:D91)</f>
         <v/>
       </c>
-      <c r="E95" s="10">
-        <f>MAX(E3:E90)</f>
+      <c r="E96" s="10">
+        <f>MAX(E3:E91)</f>
         <v/>
       </c>
-      <c r="F95" s="10">
-        <f>MAX(F3:F90)</f>
+      <c r="F96" s="10">
+        <f>MAX(F3:F91)</f>
         <v/>
       </c>
-      <c r="G95" s="10">
-        <f>MAX(G3:G90)</f>
+      <c r="G96" s="10">
+        <f>MAX(G3:G91)</f>
         <v/>
       </c>
-      <c r="H95" s="10">
-        <f>MAX(H3:H90)</f>
+      <c r="H96" s="10">
+        <f>MAX(H3:H91)</f>
         <v/>
       </c>
-      <c r="I95" s="10">
-        <f>MAX(I3:I90)</f>
+      <c r="I96" s="10">
+        <f>MAX(I3:I91)</f>
         <v/>
       </c>
-      <c r="J95" s="10">
-        <f>MAX(J3:J90)</f>
+      <c r="J96" s="10">
+        <f>MAX(J3:J91)</f>
         <v/>
       </c>
-      <c r="K95" s="10">
-        <f>MAX(K3:K90)</f>
+      <c r="K96" s="10">
+        <f>MAX(K3:K91)</f>
         <v/>
       </c>
-      <c r="L95" s="10">
-        <f>MAX(L3:L90)</f>
+      <c r="L96" s="10">
+        <f>MAX(L3:L91)</f>
         <v/>
       </c>
-      <c r="M95" s="10">
-        <f>MAX(M3:M90)</f>
+      <c r="M96" s="10">
+        <f>MAX(M3:M91)</f>
         <v/>
       </c>
     </row>
-    <row r="96">
-      <c r="C96" s="12" t="n"/>
-      <c r="D96" s="12" t="n"/>
-      <c r="E96" s="12" t="n"/>
-      <c r="F96" s="12" t="n"/>
-      <c r="G96" s="12" t="n"/>
-      <c r="H96" s="12" t="n"/>
-      <c r="I96" s="12" t="n"/>
-      <c r="J96" s="12" t="n"/>
-      <c r="K96" s="12" t="n"/>
-      <c r="L96" s="12" t="n"/>
-      <c r="M96" s="12" t="n"/>
-    </row>
     <row r="97">
-      <c r="C97" s="11" t="inlineStr">
+      <c r="C97" s="12" t="n"/>
+      <c r="D97" s="12" t="n"/>
+      <c r="E97" s="12" t="n"/>
+      <c r="F97" s="12" t="n"/>
+      <c r="G97" s="12" t="n"/>
+      <c r="H97" s="12" t="n"/>
+      <c r="I97" s="12" t="n"/>
+      <c r="J97" s="12" t="n"/>
+      <c r="K97" s="12" t="n"/>
+      <c r="L97" s="12" t="n"/>
+      <c r="M97" s="12" t="n"/>
+    </row>
+    <row r="98">
+      <c r="C98" s="11" t="inlineStr">
         <is>
           <t>MÍNIMO</t>
         </is>
       </c>
-      <c r="D97" s="10">
-        <f>MIN(D3:D90)</f>
+      <c r="D98" s="10">
+        <f>MIN(D3:D91)</f>
         <v/>
       </c>
-      <c r="E97" s="10">
-        <f>MIN(E3:E90)</f>
+      <c r="E98" s="10">
+        <f>MIN(E3:E91)</f>
         <v/>
       </c>
-      <c r="F97" s="10">
-        <f>MIN(F3:F90)</f>
+      <c r="F98" s="10">
+        <f>MIN(F3:F91)</f>
         <v/>
       </c>
-      <c r="G97" s="10">
-        <f>MIN(G3:G90)</f>
+      <c r="G98" s="10">
+        <f>MIN(G3:G91)</f>
         <v/>
       </c>
-      <c r="H97" s="10">
-        <f>MIN(H3:H90)</f>
+      <c r="H98" s="10">
+        <f>MIN(H3:H91)</f>
         <v/>
       </c>
-      <c r="I97" s="10">
-        <f>MIN(I3:I90)</f>
+      <c r="I98" s="10">
+        <f>MIN(I3:I91)</f>
         <v/>
       </c>
-      <c r="J97" s="10">
-        <f>MIN(J3:J90)</f>
+      <c r="J98" s="10">
+        <f>MIN(J3:J91)</f>
         <v/>
       </c>
-      <c r="K97" s="10">
-        <f>MIN(K3:K90)</f>
+      <c r="K98" s="10">
+        <f>MIN(K3:K91)</f>
         <v/>
       </c>
-      <c r="L97" s="10">
-        <f>MIN(L3:L90)</f>
+      <c r="L98" s="10">
+        <f>MIN(L3:L91)</f>
         <v/>
       </c>
-      <c r="M97" s="10">
-        <f>MIN(M3:M90)</f>
+      <c r="M98" s="10">
+        <f>MIN(M3:M91)</f>
         <v/>
       </c>
     </row>
-    <row r="98">
-      <c r="C98" s="12" t="n"/>
-      <c r="D98" s="12" t="n"/>
-      <c r="E98" s="12" t="n"/>
-      <c r="F98" s="12" t="n"/>
-      <c r="G98" s="12" t="n"/>
-      <c r="H98" s="12" t="n"/>
-      <c r="I98" s="12" t="n"/>
-      <c r="J98" s="12" t="n"/>
-      <c r="K98" s="12" t="n"/>
-      <c r="L98" s="12" t="n"/>
-      <c r="M98" s="12" t="n"/>
+    <row r="99">
+      <c r="C99" s="12" t="n"/>
+      <c r="D99" s="12" t="n"/>
+      <c r="E99" s="12" t="n"/>
+      <c r="F99" s="12" t="n"/>
+      <c r="G99" s="12" t="n"/>
+      <c r="H99" s="12" t="n"/>
+      <c r="I99" s="12" t="n"/>
+      <c r="J99" s="12" t="n"/>
+      <c r="K99" s="12" t="n"/>
+      <c r="L99" s="12" t="n"/>
+      <c r="M99" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="J93:J94"/>
-    <mergeCell ref="L91:L92"/>
-    <mergeCell ref="I95:I96"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="L97:L98"/>
-    <mergeCell ref="C97:C98"/>
-    <mergeCell ref="H93:H94"/>
-    <mergeCell ref="F95:F96"/>
-    <mergeCell ref="G97:G98"/>
-    <mergeCell ref="L93:L94"/>
-    <mergeCell ref="I97:I98"/>
-    <mergeCell ref="D95:D96"/>
-    <mergeCell ref="F91:F92"/>
-    <mergeCell ref="J95:J96"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="G93:G94"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="D97:D98"/>
-    <mergeCell ref="G95:G96"/>
-    <mergeCell ref="F97:F98"/>
-    <mergeCell ref="F93:F94"/>
-    <mergeCell ref="C95:C96"/>
-    <mergeCell ref="E95:E96"/>
-    <mergeCell ref="M95:M96"/>
-    <mergeCell ref="M91:M92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="D93:D94"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="E97:E98"/>
-    <mergeCell ref="K97:K98"/>
-    <mergeCell ref="M97:M98"/>
-    <mergeCell ref="M93:M94"/>
-    <mergeCell ref="H95:H96"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="L95:L96"/>
-    <mergeCell ref="J97:J98"/>
-    <mergeCell ref="E93:E94"/>
-    <mergeCell ref="K93:K94"/>
-    <mergeCell ref="H97:H98"/>
-    <mergeCell ref="K95:K96"/>
+    <mergeCell ref="E92:E93"/>
+    <mergeCell ref="K92:K93"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E98:E99"/>
+    <mergeCell ref="G98:G99"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="M98:M99"/>
+    <mergeCell ref="K94:K95"/>
+    <mergeCell ref="M94:M95"/>
+    <mergeCell ref="J98:J99"/>
+    <mergeCell ref="L92:L93"/>
+    <mergeCell ref="E94:E95"/>
+    <mergeCell ref="K96:K97"/>
+    <mergeCell ref="H98:H99"/>
+    <mergeCell ref="F94:F95"/>
+    <mergeCell ref="I92:I93"/>
+    <mergeCell ref="H94:H95"/>
+    <mergeCell ref="I96:I97"/>
+    <mergeCell ref="G92:G93"/>
+    <mergeCell ref="K98:K99"/>
+    <mergeCell ref="J94:J95"/>
+    <mergeCell ref="F96:F97"/>
+    <mergeCell ref="L94:L95"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="H96:H97"/>
+    <mergeCell ref="I98:I99"/>
+    <mergeCell ref="F92:F93"/>
+    <mergeCell ref="L96:L97"/>
+    <mergeCell ref="G94:G95"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="I94:I95"/>
+    <mergeCell ref="J96:J97"/>
+    <mergeCell ref="H92:H93"/>
+    <mergeCell ref="L98:L99"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="G96:G97"/>
+    <mergeCell ref="F98:F99"/>
+    <mergeCell ref="M96:M97"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="M92:M93"/>
+    <mergeCell ref="J92:J93"/>
+    <mergeCell ref="E96:E97"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="C92:C93"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Anexo_04_Estadisticas_post_limpieza/Anexo_04_Estadisticas_post_limpieza.xlsx
+++ b/Anexo_04_Estadisticas_post_limpieza/Anexo_04_Estadisticas_post_limpieza.xlsx
@@ -368,7 +368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:M99"/>
+  <dimension ref="A2:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="9.140625" customWidth="1" style="1" min="1" max="1"/>
@@ -3769,38 +3769,38 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>SRR26147470_clean</t>
+          <t>SRR26147481_clean</t>
         </is>
       </c>
       <c r="D86" s="4" t="n">
-        <v>7705</v>
+        <v>10820</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>11128785</v>
+        <v>15462723</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1444.36</v>
+        <v>1429.09</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>1585</v>
+        <v>1596</v>
       </c>
       <c r="I86" s="4" t="n">
-        <v>1445</v>
+        <v>1434</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>54.85</v>
+        <v>56.63</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>17.98</v>
+        <v>17.99</v>
       </c>
       <c r="L86" s="4" t="n">
-        <v>13.68</v>
+        <v>13.96</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>23.32</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="87">
@@ -3809,38 +3809,38 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>SRR26147481_clean</t>
+          <t>SRR26147483_clean</t>
         </is>
       </c>
       <c r="D87" s="4" t="n">
-        <v>10820</v>
+        <v>12492</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>15462723</v>
+        <v>17748216</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1429.09</v>
+        <v>1420.77</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>1596</v>
+        <v>1631</v>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1434</v>
+        <v>1426</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>56.63</v>
+        <v>54.17</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>17.99</v>
+        <v>18.19</v>
       </c>
       <c r="L87" s="4" t="n">
-        <v>13.96</v>
+        <v>13.79</v>
       </c>
       <c r="M87" s="4" t="n">
-        <v>23.3</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="88">
@@ -3849,38 +3849,38 @@
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>SRR26147483_clean</t>
+          <t>SRR26147494_clean</t>
         </is>
       </c>
       <c r="D88" s="4" t="n">
-        <v>12492</v>
+        <v>15742</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>17748216</v>
+        <v>22360870</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1420.77</v>
+        <v>1420.46</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>1631</v>
+        <v>1579</v>
       </c>
       <c r="I88" s="4" t="n">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>54.17</v>
+        <v>54.13</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>18.19</v>
+        <v>18.16</v>
       </c>
       <c r="L88" s="4" t="n">
-        <v>13.79</v>
+        <v>13.82</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>24.16</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="89">
@@ -3889,414 +3889,376 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>SRR26147494_clean</t>
+          <t>SRR26147505_clean</t>
         </is>
       </c>
       <c r="D89" s="4" t="n">
-        <v>15742</v>
+        <v>14426</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>22360870</v>
+        <v>20508853</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1420.46</v>
+        <v>1421.66</v>
       </c>
       <c r="G89" s="4" t="n">
         <v>1000</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>1579</v>
+        <v>1628</v>
       </c>
       <c r="I89" s="4" t="n">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>54.13</v>
+        <v>54.3</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>18.16</v>
+        <v>18.19</v>
       </c>
       <c r="L89" s="4" t="n">
         <v>13.82</v>
       </c>
       <c r="M89" s="4" t="n">
-        <v>24.2</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="11" t="n">
         <v>88</v>
       </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>SRR26147505_clean</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="n">
-        <v>14426</v>
-      </c>
-      <c r="E90" s="4" t="n">
-        <v>20508853</v>
-      </c>
-      <c r="F90" s="4" t="n">
-        <v>1421.66</v>
-      </c>
-      <c r="G90" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H90" s="4" t="n">
-        <v>1628</v>
-      </c>
-      <c r="I90" s="4" t="n">
-        <v>1426</v>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="K90" s="4" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="L90" s="4" t="n">
-        <v>13.82</v>
-      </c>
-      <c r="M90" s="4" t="n">
-        <v>24.33</v>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>SRR26147516_clean</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>20705</v>
+      </c>
+      <c r="E90" s="9" t="n">
+        <v>29564278</v>
+      </c>
+      <c r="F90" s="9" t="n">
+        <v>1427.88</v>
+      </c>
+      <c r="G90" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H90" s="9" t="n">
+        <v>1696</v>
+      </c>
+      <c r="I90" s="9" t="n">
+        <v>1432</v>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="L90" s="9" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="M90" s="9" t="n">
+        <v>23.93</v>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="11" t="n">
-        <v>89</v>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>SRR26147516_clean</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="n">
-        <v>20705</v>
-      </c>
-      <c r="E91" s="9" t="n">
-        <v>29564278</v>
-      </c>
-      <c r="F91" s="9" t="n">
-        <v>1427.88</v>
-      </c>
-      <c r="G91" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H91" s="9" t="n">
-        <v>1696</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>1432</v>
-      </c>
-      <c r="J91" s="9" t="n">
-        <v>56.56</v>
-      </c>
-      <c r="K91" s="9" t="n">
-        <v>17.94</v>
-      </c>
-      <c r="L91" s="9" t="n">
-        <v>13.91</v>
-      </c>
-      <c r="M91" s="9" t="n">
-        <v>23.93</v>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D91" s="10">
+        <f>SUM(D3:D90)</f>
+        <v/>
+      </c>
+      <c r="E91" s="10">
+        <f>SUM(E3:E90)</f>
+        <v/>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
-      <c r="C92" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D92" s="10">
-        <f>SUM(D3:D91)</f>
+      <c r="C92" s="12" t="n"/>
+      <c r="D92" s="12" t="n"/>
+      <c r="E92" s="12" t="n"/>
+      <c r="F92" s="12" t="n"/>
+      <c r="G92" s="12" t="n"/>
+      <c r="H92" s="12" t="n"/>
+      <c r="I92" s="12" t="n"/>
+      <c r="J92" s="12" t="n"/>
+      <c r="K92" s="12" t="n"/>
+      <c r="L92" s="12" t="n"/>
+      <c r="M92" s="12" t="n"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>PROMEDIO</t>
+        </is>
+      </c>
+      <c r="D93" s="10">
+        <f>AVERAGE(D3:D90)</f>
         <v/>
       </c>
-      <c r="E92" s="10">
-        <f>SUM(E3:E91)</f>
+      <c r="E93" s="10">
+        <f>AVERAGE(E3:E90)</f>
         <v/>
       </c>
-      <c r="F92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M92" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-      <c r="E93" s="12" t="n"/>
-      <c r="F93" s="12" t="n"/>
-      <c r="G93" s="12" t="n"/>
-      <c r="H93" s="12" t="n"/>
-      <c r="I93" s="12" t="n"/>
-      <c r="J93" s="12" t="n"/>
-      <c r="K93" s="12" t="n"/>
-      <c r="L93" s="12" t="n"/>
-      <c r="M93" s="12" t="n"/>
+      <c r="F93" s="10">
+        <f>AVERAGE(F3:F90)</f>
+        <v/>
+      </c>
+      <c r="G93" s="10">
+        <f>AVERAGE(G3:G90)</f>
+        <v/>
+      </c>
+      <c r="H93" s="10">
+        <f>AVERAGE(H3:H90)</f>
+        <v/>
+      </c>
+      <c r="I93" s="10">
+        <f>AVERAGE(I3:I90)</f>
+        <v/>
+      </c>
+      <c r="J93" s="10">
+        <f>AVERAGE(J3:J90)</f>
+        <v/>
+      </c>
+      <c r="K93" s="10">
+        <f>AVERAGE(K3:K90)</f>
+        <v/>
+      </c>
+      <c r="L93" s="10">
+        <f>AVERAGE(L3:L90)</f>
+        <v/>
+      </c>
+      <c r="M93" s="10">
+        <f>AVERAGE(M3:M90)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
-      <c r="C94" s="11" t="inlineStr">
-        <is>
-          <t>PROMEDIO</t>
-        </is>
-      </c>
-      <c r="D94" s="10">
-        <f>AVERAGE(D3:D91)</f>
+      <c r="C94" s="12" t="n"/>
+      <c r="D94" s="12" t="n"/>
+      <c r="E94" s="12" t="n"/>
+      <c r="F94" s="12" t="n"/>
+      <c r="G94" s="12" t="n"/>
+      <c r="H94" s="12" t="n"/>
+      <c r="I94" s="12" t="n"/>
+      <c r="J94" s="12" t="n"/>
+      <c r="K94" s="12" t="n"/>
+      <c r="L94" s="12" t="n"/>
+      <c r="M94" s="12" t="n"/>
+    </row>
+    <row r="95">
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>MÁXIMO</t>
+        </is>
+      </c>
+      <c r="D95" s="10">
+        <f>MAX(D3:D90)</f>
         <v/>
       </c>
-      <c r="E94" s="10">
-        <f>AVERAGE(E3:E91)</f>
+      <c r="E95" s="10">
+        <f>MAX(E3:E90)</f>
         <v/>
       </c>
-      <c r="F94" s="10">
-        <f>AVERAGE(F3:F91)</f>
+      <c r="F95" s="10">
+        <f>MAX(F3:F90)</f>
         <v/>
       </c>
-      <c r="G94" s="10">
-        <f>AVERAGE(G3:G91)</f>
+      <c r="G95" s="10">
+        <f>MAX(G3:G90)</f>
         <v/>
       </c>
-      <c r="H94" s="10">
-        <f>AVERAGE(H3:H91)</f>
+      <c r="H95" s="10">
+        <f>MAX(H3:H90)</f>
         <v/>
       </c>
-      <c r="I94" s="10">
-        <f>AVERAGE(I3:I91)</f>
+      <c r="I95" s="10">
+        <f>MAX(I3:I90)</f>
         <v/>
       </c>
-      <c r="J94" s="10">
-        <f>AVERAGE(J3:J91)</f>
+      <c r="J95" s="10">
+        <f>MAX(J3:J90)</f>
         <v/>
       </c>
-      <c r="K94" s="10">
-        <f>AVERAGE(K3:K91)</f>
+      <c r="K95" s="10">
+        <f>MAX(K3:K90)</f>
         <v/>
       </c>
-      <c r="L94" s="10">
-        <f>AVERAGE(L3:L91)</f>
+      <c r="L95" s="10">
+        <f>MAX(L3:L90)</f>
         <v/>
       </c>
-      <c r="M94" s="10">
-        <f>AVERAGE(M3:M91)</f>
+      <c r="M95" s="10">
+        <f>MAX(M3:M90)</f>
         <v/>
       </c>
     </row>
-    <row r="95">
-      <c r="C95" s="12" t="n"/>
-      <c r="D95" s="12" t="n"/>
-      <c r="E95" s="12" t="n"/>
-      <c r="F95" s="12" t="n"/>
-      <c r="G95" s="12" t="n"/>
-      <c r="H95" s="12" t="n"/>
-      <c r="I95" s="12" t="n"/>
-      <c r="J95" s="12" t="n"/>
-      <c r="K95" s="12" t="n"/>
-      <c r="L95" s="12" t="n"/>
-      <c r="M95" s="12" t="n"/>
-    </row>
     <row r="96">
-      <c r="C96" s="11" t="inlineStr">
-        <is>
-          <t>MÁXIMO</t>
-        </is>
-      </c>
-      <c r="D96" s="10">
-        <f>MAX(D3:D91)</f>
+      <c r="C96" s="12" t="n"/>
+      <c r="D96" s="12" t="n"/>
+      <c r="E96" s="12" t="n"/>
+      <c r="F96" s="12" t="n"/>
+      <c r="G96" s="12" t="n"/>
+      <c r="H96" s="12" t="n"/>
+      <c r="I96" s="12" t="n"/>
+      <c r="J96" s="12" t="n"/>
+      <c r="K96" s="12" t="n"/>
+      <c r="L96" s="12" t="n"/>
+      <c r="M96" s="12" t="n"/>
+    </row>
+    <row r="97">
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>MÍNIMO</t>
+        </is>
+      </c>
+      <c r="D97" s="10">
+        <f>MIN(D3:D90)</f>
         <v/>
       </c>
-      <c r="E96" s="10">
-        <f>MAX(E3:E91)</f>
+      <c r="E97" s="10">
+        <f>MIN(E3:E90)</f>
         <v/>
       </c>
-      <c r="F96" s="10">
-        <f>MAX(F3:F91)</f>
+      <c r="F97" s="10">
+        <f>MIN(F3:F90)</f>
         <v/>
       </c>
-      <c r="G96" s="10">
-        <f>MAX(G3:G91)</f>
+      <c r="G97" s="10">
+        <f>MIN(G3:G90)</f>
         <v/>
       </c>
-      <c r="H96" s="10">
-        <f>MAX(H3:H91)</f>
+      <c r="H97" s="10">
+        <f>MIN(H3:H90)</f>
         <v/>
       </c>
-      <c r="I96" s="10">
-        <f>MAX(I3:I91)</f>
+      <c r="I97" s="10">
+        <f>MIN(I3:I90)</f>
         <v/>
       </c>
-      <c r="J96" s="10">
-        <f>MAX(J3:J91)</f>
+      <c r="J97" s="10">
+        <f>MIN(J3:J90)</f>
         <v/>
       </c>
-      <c r="K96" s="10">
-        <f>MAX(K3:K91)</f>
+      <c r="K97" s="10">
+        <f>MIN(K3:K90)</f>
         <v/>
       </c>
-      <c r="L96" s="10">
-        <f>MAX(L3:L91)</f>
+      <c r="L97" s="10">
+        <f>MIN(L3:L90)</f>
         <v/>
       </c>
-      <c r="M96" s="10">
-        <f>MAX(M3:M91)</f>
+      <c r="M97" s="10">
+        <f>MIN(M3:M90)</f>
         <v/>
       </c>
     </row>
-    <row r="97">
-      <c r="C97" s="12" t="n"/>
-      <c r="D97" s="12" t="n"/>
-      <c r="E97" s="12" t="n"/>
-      <c r="F97" s="12" t="n"/>
-      <c r="G97" s="12" t="n"/>
-      <c r="H97" s="12" t="n"/>
-      <c r="I97" s="12" t="n"/>
-      <c r="J97" s="12" t="n"/>
-      <c r="K97" s="12" t="n"/>
-      <c r="L97" s="12" t="n"/>
-      <c r="M97" s="12" t="n"/>
-    </row>
     <row r="98">
-      <c r="C98" s="11" t="inlineStr">
-        <is>
-          <t>MÍNIMO</t>
-        </is>
-      </c>
-      <c r="D98" s="10">
-        <f>MIN(D3:D91)</f>
-        <v/>
-      </c>
-      <c r="E98" s="10">
-        <f>MIN(E3:E91)</f>
-        <v/>
-      </c>
-      <c r="F98" s="10">
-        <f>MIN(F3:F91)</f>
-        <v/>
-      </c>
-      <c r="G98" s="10">
-        <f>MIN(G3:G91)</f>
-        <v/>
-      </c>
-      <c r="H98" s="10">
-        <f>MIN(H3:H91)</f>
-        <v/>
-      </c>
-      <c r="I98" s="10">
-        <f>MIN(I3:I91)</f>
-        <v/>
-      </c>
-      <c r="J98" s="10">
-        <f>MIN(J3:J91)</f>
-        <v/>
-      </c>
-      <c r="K98" s="10">
-        <f>MIN(K3:K91)</f>
-        <v/>
-      </c>
-      <c r="L98" s="10">
-        <f>MIN(L3:L91)</f>
-        <v/>
-      </c>
-      <c r="M98" s="10">
-        <f>MIN(M3:M91)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="12" t="n"/>
-      <c r="F99" s="12" t="n"/>
-      <c r="G99" s="12" t="n"/>
-      <c r="H99" s="12" t="n"/>
-      <c r="I99" s="12" t="n"/>
-      <c r="J99" s="12" t="n"/>
-      <c r="K99" s="12" t="n"/>
-      <c r="L99" s="12" t="n"/>
-      <c r="M99" s="12" t="n"/>
-    </row>
+      <c r="C98" s="12" t="n"/>
+      <c r="D98" s="12" t="n"/>
+      <c r="E98" s="12" t="n"/>
+      <c r="F98" s="12" t="n"/>
+      <c r="G98" s="12" t="n"/>
+      <c r="H98" s="12" t="n"/>
+      <c r="I98" s="12" t="n"/>
+      <c r="J98" s="12" t="n"/>
+      <c r="K98" s="12" t="n"/>
+      <c r="L98" s="12" t="n"/>
+      <c r="M98" s="12" t="n"/>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="E92:E93"/>
-    <mergeCell ref="K92:K93"/>
-    <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E98:E99"/>
-    <mergeCell ref="G98:G99"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="M98:M99"/>
-    <mergeCell ref="K94:K95"/>
-    <mergeCell ref="M94:M95"/>
-    <mergeCell ref="J98:J99"/>
-    <mergeCell ref="L92:L93"/>
-    <mergeCell ref="E94:E95"/>
-    <mergeCell ref="K96:K97"/>
-    <mergeCell ref="H98:H99"/>
-    <mergeCell ref="F94:F95"/>
-    <mergeCell ref="I92:I93"/>
-    <mergeCell ref="H94:H95"/>
-    <mergeCell ref="I96:I97"/>
-    <mergeCell ref="G92:G93"/>
-    <mergeCell ref="K98:K99"/>
-    <mergeCell ref="J94:J95"/>
-    <mergeCell ref="F96:F97"/>
-    <mergeCell ref="L94:L95"/>
-    <mergeCell ref="D92:D93"/>
-    <mergeCell ref="H96:H97"/>
-    <mergeCell ref="I98:I99"/>
-    <mergeCell ref="F92:F93"/>
-    <mergeCell ref="L96:L97"/>
-    <mergeCell ref="G94:G95"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="I94:I95"/>
-    <mergeCell ref="J96:J97"/>
-    <mergeCell ref="H92:H93"/>
-    <mergeCell ref="L98:L99"/>
-    <mergeCell ref="D98:D99"/>
-    <mergeCell ref="G96:G97"/>
-    <mergeCell ref="F98:F99"/>
-    <mergeCell ref="M96:M97"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="M92:M93"/>
-    <mergeCell ref="J92:J93"/>
-    <mergeCell ref="E96:E97"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="J93:J94"/>
+    <mergeCell ref="L91:L92"/>
+    <mergeCell ref="I95:I96"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="K91:K92"/>
+    <mergeCell ref="L97:L98"/>
+    <mergeCell ref="H93:H94"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="C97:C98"/>
+    <mergeCell ref="G97:G98"/>
+    <mergeCell ref="L93:L94"/>
+    <mergeCell ref="I97:I98"/>
+    <mergeCell ref="D95:D96"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="J95:J96"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="G93:G94"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="D97:D98"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="F97:F98"/>
+    <mergeCell ref="F93:F94"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="M95:M96"/>
+    <mergeCell ref="M91:M92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="D93:D94"/>
+    <mergeCell ref="E97:E98"/>
+    <mergeCell ref="K97:K98"/>
+    <mergeCell ref="M97:M98"/>
+    <mergeCell ref="M93:M94"/>
+    <mergeCell ref="H95:H96"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="L95:L96"/>
+    <mergeCell ref="J97:J98"/>
+    <mergeCell ref="K93:K94"/>
+    <mergeCell ref="E93:E94"/>
+    <mergeCell ref="H97:H98"/>
+    <mergeCell ref="K95:K96"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
